--- a/datos/Semana28.xlsx
+++ b/datos/Semana28.xlsx
@@ -610,7 +610,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46177</v>
+        <v>46207</v>
       </c>
       <c r="B3" s="3">
         <v>10033308</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46177</v>
+        <v>46207</v>
       </c>
       <c r="B4" s="3">
         <v>10033301</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="B5" s="3">
         <v>10033304</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="B6" s="3">
         <v>10033302</v>
@@ -688,7 +688,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="B7" s="3">
         <v>10033303</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="B8" s="3">
         <v>10033192</v>
@@ -726,7 +726,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B9" s="3">
         <v>10033314</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B10" s="3">
         <v>10033349</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B11" s="3">
         <v>10032361</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B12" s="3">
         <v>10032364</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B13" s="3">
         <v>10032365</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="B14" s="3">
         <v>10032371</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="B15" s="3">
         <v>10033350</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="B16" s="3">
         <v>10033337</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="B17" s="3">
         <v>10032287</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="B18" s="3">
         <v>10033351</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B19" s="3">
         <v>10033347</v>
@@ -955,7 +955,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B20" s="3">
         <v>10033345</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B21" s="3">
         <v>10032361</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B22" s="3">
         <v>10032364</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B23" s="3">
         <v>10032365</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B24" s="3">
         <v>10032371</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B25" s="3">
         <v>10032110</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B26" s="6">
         <v>10032301</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B27" s="3">
         <v>10033347</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B28" s="3">
         <v>10033310</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B29" s="3">
         <v>10032367</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B30" s="3">
         <v>10032368</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="B31" s="3">
         <v>10033351</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="B32" s="3">
         <v>10033353</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>46184</v>
+        <v>46214</v>
       </c>
       <c r="B33" s="3">
         <v>10033352</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>46184</v>
+        <v>46214</v>
       </c>
       <c r="B34" s="3">
         <v>10032761</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>46185</v>
+        <v>46214</v>
       </c>
       <c r="B35" s="3">
         <v>10033392</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>46185</v>
+        <v>46214</v>
       </c>
       <c r="B36" s="3">
         <v>10033349</v>
